--- a/artfynd/A 58169-2025 artfynd.xlsx
+++ b/artfynd/A 58169-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130962874</v>
+        <v>130960611</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Effaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445987</v>
+        <v>446240</v>
       </c>
       <c r="R2" t="n">
-        <v>6759938</v>
+        <v>6759818</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,11 +756,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>I grov gammal tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130963946</v>
+        <v>130960789</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Effaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445926</v>
+        <v>446284</v>
       </c>
       <c r="R3" t="n">
-        <v>6760113</v>
+        <v>6759886</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130961057</v>
+        <v>130960843</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Effaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446138</v>
+        <v>446247</v>
       </c>
       <c r="R4" t="n">
-        <v>6759967</v>
+        <v>6759903</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,50 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130960607</v>
+        <v>130961060</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Effaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446240</v>
+        <v>446138</v>
       </c>
       <c r="R5" t="n">
-        <v>6759818</v>
+        <v>6759967</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,14 +1103,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130963816</v>
+        <v>130961105</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445932</v>
+        <v>446124</v>
       </c>
       <c r="R6" t="n">
-        <v>6760079</v>
+        <v>6759989</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,12 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt i närområdet</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,14 +1210,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130961458</v>
+        <v>130961219</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1275,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446059</v>
+        <v>446122</v>
       </c>
       <c r="R7" t="n">
-        <v>6760088</v>
+        <v>6760020</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,14 +1317,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130961962</v>
+        <v>130961428</v>
       </c>
       <c r="B8" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1382,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446084</v>
+        <v>446059</v>
       </c>
       <c r="R8" t="n">
-        <v>6759981</v>
+        <v>6760088</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,14 +1424,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130962883</v>
+        <v>130961461</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1489,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445987</v>
+        <v>446088</v>
       </c>
       <c r="R9" t="n">
-        <v>6759938</v>
+        <v>6760088</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,50 +1531,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130960395</v>
+        <v>130961750</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Effaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446272</v>
+        <v>446098</v>
       </c>
       <c r="R10" t="n">
-        <v>6759739</v>
+        <v>6760061</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1647,6 +1612,11 @@
       <c r="AB10" t="inlineStr">
         <is>
           <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,32 +1643,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130961179</v>
+        <v>130961962</v>
       </c>
       <c r="B11" t="n">
-        <v>79864</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446122</v>
+        <v>446084</v>
       </c>
       <c r="R11" t="n">
-        <v>6760020</v>
+        <v>6759981</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1754,11 +1724,6 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på stam i bakgrund</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,50 +1750,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130961218</v>
+        <v>130962090</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Effaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446122</v>
+        <v>446080</v>
       </c>
       <c r="R12" t="n">
-        <v>6760020</v>
+        <v>6759960</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,14 +1857,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130961060</v>
+        <v>130962676</v>
       </c>
       <c r="B13" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1932,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446138</v>
+        <v>446038</v>
       </c>
       <c r="R13" t="n">
-        <v>6759967</v>
+        <v>6759945</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,14 +1964,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130963950</v>
+        <v>130962883</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2039,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445926</v>
+        <v>445987</v>
       </c>
       <c r="R14" t="n">
-        <v>6760113</v>
+        <v>6759938</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2074,7 +2034,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2084,7 +2044,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2111,14 +2071,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130961105</v>
+        <v>130963816</v>
       </c>
       <c r="B15" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2146,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446124</v>
+        <v>445932</v>
       </c>
       <c r="R15" t="n">
-        <v>6759989</v>
+        <v>6760079</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2181,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2191,7 +2151,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2221,11 +2186,11 @@
         <v>130963873</v>
       </c>
       <c r="B16" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2325,32 +2290,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130961956</v>
+        <v>130963950</v>
       </c>
       <c r="B17" t="n">
-        <v>79864</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2360,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446084</v>
+        <v>445926</v>
       </c>
       <c r="R17" t="n">
-        <v>6759981</v>
+        <v>6760113</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,7 +2360,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2405,12 +2370,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2437,14 +2397,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130960789</v>
+        <v>130963976</v>
       </c>
       <c r="B18" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2472,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446284</v>
+        <v>445929</v>
       </c>
       <c r="R18" t="n">
-        <v>6759886</v>
+        <v>6760099</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2507,7 +2467,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2517,7 +2477,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2544,14 +2509,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130960843</v>
+        <v>130964305</v>
       </c>
       <c r="B19" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2579,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446247</v>
+        <v>445980</v>
       </c>
       <c r="R19" t="n">
-        <v>6759903</v>
+        <v>6759927</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2614,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2624,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2651,50 +2616,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130960378</v>
+        <v>130964752</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Effaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446272</v>
+        <v>446129</v>
       </c>
       <c r="R20" t="n">
-        <v>6759739</v>
+        <v>6759886</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2726,7 +2686,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2736,7 +2696,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2763,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130960631</v>
+        <v>130961179</v>
       </c>
       <c r="B21" t="n">
-        <v>79245</v>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2774,21 +2734,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2798,10 +2758,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446240</v>
+        <v>446122</v>
       </c>
       <c r="R21" t="n">
-        <v>6759818</v>
+        <v>6760020</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2844,6 +2804,11 @@
       <c r="AB21" t="inlineStr">
         <is>
           <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på stam i bakgrund</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2870,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130962722</v>
+        <v>130961956</v>
       </c>
       <c r="B22" t="n">
-        <v>79864</v>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2905,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446008</v>
+        <v>446084</v>
       </c>
       <c r="R22" t="n">
-        <v>6759948</v>
+        <v>6759981</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2951,6 +2916,11 @@
       <c r="AB22" t="inlineStr">
         <is>
           <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2977,10 +2947,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130963976</v>
+        <v>130962640</v>
       </c>
       <c r="B23" t="n">
-        <v>79245</v>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2988,21 +2958,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3012,10 +2982,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445929</v>
+        <v>446038</v>
       </c>
       <c r="R23" t="n">
-        <v>6760099</v>
+        <v>6759945</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3047,7 +3017,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3057,12 +3027,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3089,10 +3054,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130962640</v>
+        <v>130962722</v>
       </c>
       <c r="B24" t="n">
-        <v>79864</v>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3124,10 +3089,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446038</v>
+        <v>446008</v>
       </c>
       <c r="R24" t="n">
-        <v>6759945</v>
+        <v>6759948</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3196,14 +3161,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130961746</v>
+        <v>130960932</v>
       </c>
       <c r="B25" t="n">
-        <v>57881</v>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3236,10 +3201,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446098</v>
+        <v>446207</v>
       </c>
       <c r="R25" t="n">
-        <v>6760061</v>
+        <v>6759823</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3308,45 +3273,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130962090</v>
+        <v>130961746</v>
       </c>
       <c r="B26" t="n">
-        <v>79245</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Effaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446080</v>
+        <v>446098</v>
       </c>
       <c r="R26" t="n">
-        <v>6759960</v>
+        <v>6760061</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3418,11 +3388,11 @@
         <v>130963807</v>
       </c>
       <c r="B27" t="n">
-        <v>57881</v>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3527,10 +3497,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130961461</v>
+        <v>130960378</v>
       </c>
       <c r="B28" t="n">
-        <v>79245</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3538,34 +3508,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Effaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446088</v>
+        <v>446272</v>
       </c>
       <c r="R28" t="n">
-        <v>6760088</v>
+        <v>6759739</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3634,10 +3609,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130961750</v>
+        <v>130960607</v>
       </c>
       <c r="B29" t="n">
-        <v>79245</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3645,34 +3620,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Effaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446098</v>
+        <v>446240</v>
       </c>
       <c r="R29" t="n">
-        <v>6760061</v>
+        <v>6759818</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3715,11 +3695,6 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3746,10 +3721,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130962736</v>
+        <v>130961057</v>
       </c>
       <c r="B30" t="n">
-        <v>79835</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3757,34 +3732,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Effaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446008</v>
+        <v>446138</v>
       </c>
       <c r="R30" t="n">
-        <v>6759948</v>
+        <v>6759967</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3853,10 +3833,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130964752</v>
+        <v>130961218</v>
       </c>
       <c r="B31" t="n">
-        <v>79245</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3864,34 +3844,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Effaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446129</v>
+        <v>446122</v>
       </c>
       <c r="R31" t="n">
-        <v>6759886</v>
+        <v>6760020</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3923,7 +3908,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3933,7 +3918,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3960,10 +3945,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130964305</v>
+        <v>130962874</v>
       </c>
       <c r="B32" t="n">
-        <v>79245</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3971,34 +3956,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Effaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445980</v>
+        <v>445987</v>
       </c>
       <c r="R32" t="n">
-        <v>6759927</v>
+        <v>6759938</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4030,7 +4020,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4040,7 +4030,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>I grov gammal tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4067,10 +4062,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130961219</v>
+        <v>130963946</v>
       </c>
       <c r="B33" t="n">
-        <v>79245</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4078,34 +4073,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Effaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446122</v>
+        <v>445926</v>
       </c>
       <c r="R33" t="n">
-        <v>6760020</v>
+        <v>6760113</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4174,10 +4174,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130962676</v>
+        <v>130964300</v>
       </c>
       <c r="B34" t="n">
-        <v>79245</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4185,34 +4185,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Effaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446038</v>
+        <v>445980</v>
       </c>
       <c r="R34" t="n">
-        <v>6759945</v>
+        <v>6759927</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4244,7 +4249,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4254,7 +4259,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4281,38 +4286,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130964300</v>
+        <v>130960395</v>
       </c>
       <c r="B35" t="n">
-        <v>57884</v>
+        <v>8455</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4321,10 +4326,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445980</v>
+        <v>446272</v>
       </c>
       <c r="R35" t="n">
-        <v>6759927</v>
+        <v>6759739</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4356,7 +4361,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4366,7 +4371,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4390,6 +4395,113 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130962736</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Effaråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>446008</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6759948</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58169-2025 artfynd.xlsx
+++ b/artfynd/A 58169-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130960611</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130960789</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130960843</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130961060</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130961105</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130961219</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130961428</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130961461</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130961750</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130961962</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1854,6 +1909,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962090</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1961,6 +2021,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962676</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2068,6 +2133,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962883</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2180,6 +2250,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130963816</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2287,6 +2362,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130963873</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2394,6 +2474,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130963950</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2506,6 +2591,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130963976</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2613,6 +2703,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964305</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2720,6 +2815,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964752</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2832,6 +2932,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130961179</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2944,6 +3049,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130961956</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3051,6 +3161,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962640</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3158,6 +3273,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962722</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3270,6 +3390,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130960932</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3382,6 +3507,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130961746</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3494,6 +3624,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130963807</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3606,6 +3741,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130960378</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3718,6 +3858,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130960607</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3830,6 +3975,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130961057</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3942,6 +4092,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130961218</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4059,6 +4214,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962874</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4171,6 +4331,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130963946</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4283,6 +4448,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964300</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4395,6 +4565,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130960395</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4502,8 +4677,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962736</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>